--- a/dados/tabelas/resumo_cenario_algoritmo.xlsx
+++ b/dados/tabelas/resumo_cenario_algoritmo.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,37 +429,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cenário</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Algoritmo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>media_bitrate_kbps</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mediana_bitrate_kbps</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>media_buffer_s</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>travamentos_totais</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>taxa_travamento_pct</t>
         </is>
@@ -465,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>732.5</v>
+        <v>715</v>
       </c>
       <c r="D2" t="n">
         <v>500</v>
       </c>
       <c r="E2" t="n">
-        <v>3.27</v>
+        <v>2.27</v>
       </c>
       <c r="F2" t="n">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="G2" t="n">
-        <v>24.33</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1350</v>
+        <v>940</v>
       </c>
       <c r="D3" t="n">
         <v>500</v>
       </c>
       <c r="E3" t="n">
-        <v>1.31</v>
+        <v>0.99</v>
       </c>
       <c r="F3" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="G3" t="n">
-        <v>36.67</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -519,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2418.33</v>
+        <v>6096.67</v>
       </c>
       <c r="D4" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="E4" t="n">
-        <v>11.74</v>
+        <v>17.51</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -546,19 +558,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2338.33</v>
+        <v>5553.33</v>
       </c>
       <c r="D5" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>11.74</v>
+        <v>9.5</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>5.33</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="6">
@@ -573,13 +585,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1608.33</v>
+        <v>1765</v>
       </c>
       <c r="D6" t="n">
         <v>1500</v>
       </c>
       <c r="E6" t="n">
-        <v>10.12</v>
+        <v>8.92</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -600,19 +612,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2216.67</v>
+        <v>3633.33</v>
       </c>
       <c r="D7" t="n">
         <v>1500</v>
       </c>
       <c r="E7" t="n">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="F7" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="G7" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
     </row>
   </sheetData>
